--- a/order_forms/027_custom_sticker_order_form--order_forms.xlsx
+++ b/order_forms/027_custom_sticker_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>custom_sticker_order_form</t>
+          <t>order_details</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sticker Order Form</t>
+          <t>Order Details</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,35 +543,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>sticker_quantity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Sticker Quantity</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sticker_design</t>
+          <t>shipping_address</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sticker Design</t>
+          <t>Shipping Address</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>quantity_of_stickers</t>
+          <t>shipping_phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Quantity of Stickers</t>
+          <t>Shipping Phone</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>custom_sticker_order_form</t>
+          <t>shipping_email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Custom Sticker Order Form</t>
+          <t>Shipping Email</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sticker_size</t>
+          <t>billing_name</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sticker Size</t>
+          <t>Billing Name</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>shipping_address</t>
+          <t>billing_address</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shipping Address</t>
+          <t>Billing Address</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>order_details</t>
+          <t>billing_phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Order Details</t>
+          <t>Billing Phone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>shipping_phone</t>
+          <t>billing_email</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shipping Phone</t>
+          <t>Billing Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>shipping_email</t>
+          <t>order_total</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Shipping Email</t>
+          <t>Order Total</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>billing_name</t>
+          <t>shipping_city</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Billing Name</t>
+          <t>Shipping City</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>billing_phone</t>
+          <t>shipping_state</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Billing Phone</t>
+          <t>Shipping State</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>billing_email</t>
+          <t>shipping_zip</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Billing Email</t>
+          <t>Shipping Zip</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>order_total</t>
+          <t>shipping_country</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Order Total</t>
+          <t>Shipping Country</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>custom_sticker_order_form</t>
+          <t>billing_city</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Custom Sticker Order Form</t>
+          <t>Billing City</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>custom_sticker_order_form</t>
+          <t>billing_state</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Custom Sticker Order Form</t>
+          <t>Billing State</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>custom_sticker_order_form</t>
+          <t>billing_zip</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Custom Sticker Order Form</t>
+          <t>Billing Zip</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>shipping_city</t>
+          <t>billing_country</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Shipping City</t>
+          <t>Billing Country</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,276 +929,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>shipping_state</t>
+          <t>sticker_design</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shipping State</t>
+          <t>Sticker Design</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>shipping_zip</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Shipping Zip</t>
+          <t>Payment Method</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Custom Sticker Order Form</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Custom Sticker Order Form</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Custom Sticker Order Form</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>shipping_country</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Shipping Country</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>billing_address</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Billing Address</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>billing_city</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Billing City</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>billing_state</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Billing State</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>billing_zip</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Billing Zip</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>billing_country</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Billing Country</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Custom Sticker Order Form</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1213,10 +983,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1241,7 +1011,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>custom_sticker_order_form_choices</t>
+          <t>sticker_design_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1258,7 +1028,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>custom_sticker_order_form_choices</t>
+          <t>sticker_design_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1275,7 +1045,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sticker_design_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1292,7 +1062,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sticker_design_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1301,312 +1071,6 @@
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>sticker_size_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>sticker_size_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>custom_sticker_order_form_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
